--- a/survey_templates/033_social_movements_and_their_impact_survey--survey_templates.xlsx
+++ b/survey_templates/033_social_movements_and_their_impact_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'labor'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Labor'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'civil_rights'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Civil Rights'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'environmental'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Environmental'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'social_change'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Social Change'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'economic'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Economic'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'social'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Social'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'environmental'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Environmental'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'positive'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Positive'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'negative'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Negative'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'neutral'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Neutral'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'men'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'Men'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'women'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'Women'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'both'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'Both'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
